--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769759</v>
+        <v>129769044</v>
       </c>
       <c r="B5" t="n">
         <v>58106</v>
@@ -1065,12 +1065,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1084,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512216</v>
+        <v>512196</v>
       </c>
       <c r="R5" t="n">
-        <v>6294754</v>
+        <v>6294688</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1155,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769044</v>
+        <v>129769759</v>
       </c>
       <c r="B6" t="n">
         <v>58106</v>
@@ -1185,17 +1190,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512196</v>
+        <v>512216</v>
       </c>
       <c r="R6" t="n">
-        <v>6294688</v>
+        <v>6294754</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769044</v>
+        <v>129769759</v>
       </c>
       <c r="B5" t="n">
         <v>58106</v>
@@ -1065,17 +1065,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512196</v>
+        <v>512216</v>
       </c>
       <c r="R5" t="n">
-        <v>6294688</v>
+        <v>6294754</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1160,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769759</v>
+        <v>129769044</v>
       </c>
       <c r="B6" t="n">
         <v>58106</v>
@@ -1190,12 +1185,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512216</v>
+        <v>512196</v>
       </c>
       <c r="R6" t="n">
-        <v>6294754</v>
+        <v>6294688</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129769044</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129769759</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769044</v>
+        <v>129769759</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,17 +1065,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512196</v>
+        <v>512216</v>
       </c>
       <c r="R5" t="n">
-        <v>6294688</v>
+        <v>6294754</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1160,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769759</v>
+        <v>129769044</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,12 +1185,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512216</v>
+        <v>512196</v>
       </c>
       <c r="R6" t="n">
-        <v>6294754</v>
+        <v>6294688</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769759</v>
+        <v>129769044</v>
       </c>
       <c r="B5" t="n">
         <v>58111</v>
@@ -1065,12 +1065,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1084,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512216</v>
+        <v>512196</v>
       </c>
       <c r="R5" t="n">
-        <v>6294754</v>
+        <v>6294688</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1155,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769044</v>
+        <v>129769759</v>
       </c>
       <c r="B6" t="n">
         <v>58111</v>
@@ -1185,17 +1190,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512196</v>
+        <v>512216</v>
       </c>
       <c r="R6" t="n">
-        <v>6294688</v>
+        <v>6294754</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769747</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129770319</v>
       </c>
       <c r="B4" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769044</v>
+        <v>129769759</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,17 +1065,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512196</v>
+        <v>512216</v>
       </c>
       <c r="R5" t="n">
-        <v>6294688</v>
+        <v>6294754</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1160,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769759</v>
+        <v>129769044</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,12 +1185,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512216</v>
+        <v>512196</v>
       </c>
       <c r="R6" t="n">
-        <v>6294754</v>
+        <v>6294688</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129769756</v>
       </c>
       <c r="B2" t="n">
-        <v>92289</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769747</v>
+        <v>129770319</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512231</v>
+        <v>512217</v>
       </c>
       <c r="R3" t="n">
-        <v>6294737</v>
+        <v>6294743</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770319</v>
+        <v>129769747</v>
       </c>
       <c r="B4" t="n">
-        <v>92289</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,26 +926,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512217</v>
+        <v>512231</v>
       </c>
       <c r="R4" t="n">
-        <v>6294743</v>
+        <v>6294737</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
         <v>129769044</v>
       </c>
       <c r="B5" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769759</v>
+        <v>129769176</v>
       </c>
       <c r="B6" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,27 +1190,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Ekerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R6" t="n">
-        <v>6294754</v>
+        <v>6294685</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1269,255 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129769570</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512199</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6294842</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129769759</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512216</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6294754</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Johan Thulin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>

--- a/artfynd/A 52542-2025 artfynd.xlsx
+++ b/artfynd/A 52542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769756</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129770319</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769747</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,6 +1432,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769570</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1522,8 +1557,22 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769759</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>